--- a/4_results_excel/summary_comparison_rj_vs_nonrj.xlsx
+++ b/4_results_excel/summary_comparison_rj_vs_nonrj.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Battuto\Desktop\malenia\supplementary_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadik\My Drive\Operation\ocean\Prall_etal.DiscretePrediction.CommunicationsBiology\4_results_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF327360-E93F-49AF-B1E5-1627B265A218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8279E366-28C5-4E65-9B9E-0DB54F885AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="2" r:id="rId1"/>
@@ -716,19 +716,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68053A4E-B426-4D02-A5F1-14665BC27170}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="110" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>50</v>
       </c>
       <c r="B1" s="15"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -736,7 +736,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -744,72 +744,72 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>51</v>
       </c>
@@ -817,7 +817,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>52</v>
       </c>
@@ -825,7 +825,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>53</v>
       </c>
@@ -833,22 +833,22 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B21" s="9" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>54</v>
       </c>
@@ -856,7 +856,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>55</v>
       </c>
@@ -864,7 +864,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>64</v>
       </c>
@@ -872,17 +872,17 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B27" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
         <v>30</v>
       </c>
@@ -898,18 +898,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD44F911-1668-46D7-8E1E-8B1B07959405}">
   <dimension ref="A1:I53"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" customWidth="1"/>
-    <col min="3" max="4" width="12.26953125" customWidth="1"/>
-    <col min="5" max="5" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="0.81640625" customWidth="1"/>
-    <col min="7" max="8" width="12.1796875" customWidth="1"/>
-    <col min="9" max="9" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="4" width="12.21875" customWidth="1"/>
+    <col min="5" max="5" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="0.77734375" customWidth="1"/>
+    <col min="7" max="8" width="12.21875" customWidth="1"/>
+    <col min="9" max="9" width="7.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>48</v>
       </c>
@@ -922,7 +922,7 @@
       <c r="H1" s="15"/>
       <c r="I1" s="15"/>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -949,7 +949,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -978,7 +978,7 @@
         <v>1.8104773289923937</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>1.144631729887261</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>1.0237332397027488</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>1.2903105125228824</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1094,7 +1094,7 @@
         <v>1.18181745129267</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>0.96204799996758572</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>1.7694835921486247</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>1.2147173600699408</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>1.0566055411711284</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>1.694401680694976</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>0.99759594942146579</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>0.98617838897273269</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>17</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>1.0072386900784573</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>49</v>
       </c>
@@ -1357,38 +1357,38 @@
         <v>1.2610000645703676</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>58</v>
       </c>
       <c r="B17" s="15"/>
       <c r="C17" s="14">
-        <f>2*_xlfn.STDEV.S(C3:C14)/COUNT(C3:C14)</f>
-        <v>1.3785598240744689E-2</v>
+        <f>2*_xlfn.STDEV.S(C3:C14)/SQRT(COUNT(C3:C14))</f>
+        <v>4.7754713131403864E-2</v>
       </c>
       <c r="D17" s="14">
-        <f t="shared" ref="D17:I17" si="3">2*_xlfn.STDEV.S(D3:D14)/COUNT(D3:D14)</f>
-        <v>1.2757053901368616E-2</v>
+        <f t="shared" ref="D17:E17" si="3">2*_xlfn.STDEV.S(D3:D14)/SQRT(COUNT(D3:D14))</f>
+        <v>4.4191731024130418E-2</v>
       </c>
       <c r="E17" s="14">
         <f t="shared" si="3"/>
-        <v>3.6971585686147545E-3</v>
+        <v>1.280733296895876E-2</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="14">
-        <f t="shared" si="3"/>
-        <v>2.6177565372446084E-2</v>
+        <f>2*_xlfn.STDEV.S(G3:G14)/SQRT(COUNT(G3:G14))</f>
+        <v>9.0681746487064632E-2</v>
       </c>
       <c r="H17" s="14">
-        <f t="shared" si="3"/>
-        <v>2.8626119229805857E-2</v>
+        <f t="shared" ref="H17:I17" si="4">2*_xlfn.STDEV.S(H3:H14)/SQRT(COUNT(H3:H14))</f>
+        <v>9.9163785859096409E-2</v>
       </c>
       <c r="I17" s="14">
-        <f t="shared" si="3"/>
-        <v>5.2788028444060164E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>0.18286309459300656</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
         <v>62</v>
       </c>
@@ -1401,7 +1401,7 @@
       <c r="H19" s="15"/>
       <c r="I19" s="15"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>0</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>1.5209061543403506</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>0.77300000000000002</v>
       </c>
       <c r="E22" s="10">
-        <f t="shared" ref="E22:E33" si="4">D22-C22</f>
+        <f t="shared" ref="E22:E33" si="5">D22-C22</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="F22" s="10"/>
@@ -1482,11 +1482,11 @@
         <v>0.27575350158650702</v>
       </c>
       <c r="I22" s="10">
-        <f t="shared" ref="I22:I33" si="5">G22/H22</f>
+        <f t="shared" ref="I22:I33" si="6">G22/H22</f>
         <v>1.3587994776078838</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -1500,7 +1500,7 @@
         <v>0.66800000000000004</v>
       </c>
       <c r="E23" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.0000000000000071E-3</v>
       </c>
       <c r="F23" s="10"/>
@@ -1511,11 +1511,11 @@
         <v>0.54645280140914199</v>
       </c>
       <c r="I23" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.0529080251427931</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>0.83799999999999997</v>
       </c>
       <c r="E24" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.7999999999999914E-2</v>
       </c>
       <c r="F24" s="10"/>
@@ -1540,11 +1540,11 @@
         <v>0.12897038129696001</v>
       </c>
       <c r="I24" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.4028237612227683</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>0.85699999999999998</v>
       </c>
       <c r="E25" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.0000000000000044E-3</v>
       </c>
       <c r="F25" s="10"/>
@@ -1569,11 +1569,11 @@
         <v>0.10925714146527399</v>
       </c>
       <c r="I25" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.2169482795538291</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>0.74199999999999999</v>
       </c>
       <c r="E26" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-4.0000000000000036E-3</v>
       </c>
       <c r="F26" s="10"/>
@@ -1598,11 +1598,11 @@
         <v>0.34108284917889597</v>
       </c>
       <c r="I26" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.0921510972048247</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>0.873</v>
       </c>
       <c r="E27" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.5000000000000013E-2</v>
       </c>
       <c r="F27" s="10"/>
@@ -1627,11 +1627,11 @@
         <v>8.6647806725672197E-2</v>
       </c>
       <c r="I27" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.4556679825720482</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>22</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>0.79500000000000004</v>
       </c>
       <c r="E28" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.300000000000002E-2</v>
       </c>
       <c r="F28" s="10"/>
@@ -1656,11 +1656,11 @@
         <v>0.2376230736302605</v>
       </c>
       <c r="I28" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.2416414276119305</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>23</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>0.70699999999999996</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.0000000000000044E-3</v>
       </c>
       <c r="F29" s="10"/>
@@ -1685,11 +1685,11 @@
         <v>0.42312004334688502</v>
       </c>
       <c r="I29" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.0714299759467245</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>24</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>0.90500000000000003</v>
       </c>
       <c r="E30" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.8000000000000016E-2</v>
       </c>
       <c r="F30" s="10"/>
@@ -1714,11 +1714,11 @@
         <v>5.5512709930258801E-2</v>
       </c>
       <c r="I30" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.365483931725046</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>0.85599999999999998</v>
       </c>
       <c r="E31" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.0000000000000018E-3</v>
       </c>
       <c r="F31" s="10"/>
@@ -1743,11 +1743,11 @@
         <v>0.12613043801065199</v>
       </c>
       <c r="I31" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.95068988956801026</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>0.80200000000000005</v>
       </c>
       <c r="E32" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.2000000000000011E-2</v>
       </c>
       <c r="F32" s="10"/>
@@ -1772,11 +1772,11 @@
         <v>0.20456791849881351</v>
       </c>
       <c r="I32" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.98801872102874366</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
         <v>17</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>0.51700000000000002</v>
       </c>
       <c r="E33" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.0000000000000009E-3</v>
       </c>
       <c r="F33" s="10"/>
@@ -1801,11 +1801,11 @@
         <v>0.68915515929040805</v>
       </c>
       <c r="I33" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.99423040178102406</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
         <v>49</v>
       </c>
@@ -1815,59 +1815,59 @@
         <v>0.79833333333333323</v>
       </c>
       <c r="D34" s="14">
-        <f t="shared" ref="D34:E34" si="6">AVERAGE(D21:D32)</f>
+        <f t="shared" ref="D34:E34" si="7">AVERAGE(D21:D32)</f>
         <v>0.80958333333333332</v>
       </c>
       <c r="E34" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.1250000000000001E-2</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="14">
-        <f t="shared" ref="G34:I34" si="7">AVERAGE(G21:G32)</f>
+        <f t="shared" ref="G34:I34" si="8">AVERAGE(G21:G32)</f>
         <v>0.25159788732988569</v>
       </c>
       <c r="H34" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.21730744649284639</v>
       </c>
       <c r="I34" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.2264557269604131</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="15" t="s">
         <v>58</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="14">
-        <f>2*_xlfn.STDEV.S(C21:C32)/COUNT(C21:C32)</f>
-        <v>1.2142739721583758E-2</v>
+        <f>2*_xlfn.STDEV.S(C21:C32)/SQRT(COUNT(C21:C32))</f>
+        <v>4.2063684281735667E-2</v>
       </c>
       <c r="D35" s="14">
-        <f t="shared" ref="D35:E35" si="8">2*_xlfn.STDEV.S(D21:D32)/COUNT(D21:D32)</f>
-        <v>1.2620821807538646E-2</v>
+        <f t="shared" ref="D35:E35" si="9">2*_xlfn.STDEV.S(D21:D32)/SQRT(COUNT(D21:D32))</f>
+        <v>4.3719809207860422E-2</v>
       </c>
       <c r="E35" s="14">
-        <f t="shared" si="8"/>
-        <v>1.4993685539606515E-3</v>
+        <f t="shared" si="9"/>
+        <v>5.1939650294618523E-3</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="14">
-        <f t="shared" ref="G35:I35" si="9">2*_xlfn.STDEV.S(G21:G32)/COUNT(G21:G32)</f>
-        <v>2.6715737878627587E-2</v>
+        <f>2*_xlfn.STDEV.S(G21:G32)/SQRT(COUNT(G21:G32))</f>
+        <v>9.2546030734950713E-2</v>
       </c>
       <c r="H35" s="14">
-        <f t="shared" si="9"/>
-        <v>2.5721731571531663E-2</v>
+        <f>2*_xlfn.STDEV.S(H21:H32)/SQRT(COUNT(H21:H32))</f>
+        <v>8.9102691881082607E-2</v>
       </c>
       <c r="I35" s="14">
-        <f t="shared" si="9"/>
-        <v>3.2278703758256463E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+        <f>2*_xlfn.STDEV.S(I21:I32)/SQRT(COUNT(I21:I32))</f>
+        <v>0.11181670982352933</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
         <v>63</v>
       </c>
@@ -1880,7 +1880,7 @@
       <c r="H37" s="15"/>
       <c r="I37" s="15"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>0</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>1</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>1.458227890049576</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>2</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>1.0925953120649357</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>19</v>
       </c>
@@ -2023,7 +2023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>1.0677622430553284</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>20</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>0.95978213013572367</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>21</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>2.1218185177051829</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -2139,7 +2139,7 @@
         <v>1.1560623669649417</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>23</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>24</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>2.0122202615698641</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>25</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>1.0389926517652714</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>26</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>0.90974395474469016</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
         <v>17</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>1.005787470290445</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="15" t="s">
         <v>49</v>
       </c>
@@ -2315,35 +2315,35 @@
         <v>1.234767110671293</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="15" t="s">
         <v>58</v>
       </c>
       <c r="B53" s="15"/>
       <c r="C53" s="14">
-        <f>2*_xlfn.STDEV.S(C39:C50)/COUNT(C39:C50)</f>
-        <v>5.2593511397105242E-3</v>
+        <f>2*_xlfn.STDEV.S(C39:C50)/SQRT(COUNT(C39:C50))</f>
+        <v>1.8218926777647818E-2</v>
       </c>
       <c r="D53" s="14">
-        <f t="shared" ref="D53:E53" si="14">2*_xlfn.STDEV.S(D39:D50)/COUNT(D39:D50)</f>
-        <v>5.2505210579971351E-3</v>
+        <f t="shared" ref="D53:E53" si="14">2*_xlfn.STDEV.S(D39:D50)/SQRT(COUNT(D39:D50))</f>
+        <v>1.8188338477322669E-2</v>
       </c>
       <c r="E53" s="14">
         <f t="shared" si="14"/>
-        <v>4.5758662773896856E-4</v>
+        <v>1.5851265762159997E-3</v>
       </c>
       <c r="F53" s="10"/>
       <c r="G53" s="14">
-        <f t="shared" ref="G53:I53" si="15">2*_xlfn.STDEV.S(G39:G50)/COUNT(G39:G50)</f>
-        <v>3.661928301377839E-3</v>
+        <f>2*_xlfn.STDEV.S(G39:G50)/SQRT(COUNT(G39:G50))</f>
+        <v>1.2685291743321626E-2</v>
       </c>
       <c r="H53" s="14">
-        <f t="shared" si="15"/>
-        <v>4.10342146539592E-3</v>
+        <f t="shared" ref="H53:I53" si="15">2*_xlfn.STDEV.S(H39:H50)/SQRT(COUNT(H39:H50))</f>
+        <v>1.421466892586894E-2</v>
       </c>
       <c r="I53" s="14">
         <f t="shared" si="15"/>
-        <v>6.8910302960357758E-2</v>
+        <v>0.23871229178460734</v>
       </c>
     </row>
   </sheetData>
@@ -2792,7 +2792,7 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C16:I17 C34:I35 C52:I53" formulaRange="1"/>
+    <ignoredError sqref="C16:I16 C34:I34 C52:I52 F17 C17:E17 G17:I17 F35 C35:E35 G35:I35 F53 C53:E53 G53:I53" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>